--- a/orders_template.xlsx
+++ b/orders_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariavaulina/flights_creator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF5FAC5-5B64-6D46-8506-A68A694FA0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C032AA96-F251-6248-B8BD-2B3AE2DFF8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,32 +21,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="84">
-  <si>
-    <t>⬛ Обязательные поля (синий фон)   ⬜ Необязательные поля (серый фон)   Строки с данными начинаются со строки 3</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
   <si>
     <t>ID заказа</t>
   </si>
   <si>
-    <t>Название рейса</t>
-  </si>
-  <si>
     <t>Наименование компании</t>
   </si>
   <si>
-    <t>ИНН</t>
-  </si>
-  <si>
-    <t>Тип компании</t>
-  </si>
-  <si>
-    <t>Страна</t>
-  </si>
-  <si>
-    <t>Валюта</t>
-  </si>
-  <si>
     <t>Налоговая ставка</t>
   </si>
   <si>
@@ -59,39 +41,12 @@
     <t>Плательщик НДС</t>
   </si>
   <si>
-    <t>Контактное лицо</t>
-  </si>
-  <si>
-    <t>Телефон</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Комментарий</t>
-  </si>
-  <si>
     <t>Пример: 1001234</t>
   </si>
   <si>
-    <t>Пример: Рейс Москва-СПб</t>
-  </si>
-  <si>
     <t>Пример: ООО Транслогистик</t>
   </si>
   <si>
-    <t>Пример: 7743013902</t>
-  </si>
-  <si>
-    <t>Пример: ООО</t>
-  </si>
-  <si>
-    <t>Пример: RU</t>
-  </si>
-  <si>
-    <t>Пример: RUB</t>
-  </si>
-  <si>
     <t>Пример: 20</t>
   </si>
   <si>
@@ -104,15 +59,6 @@
     <t>Да</t>
   </si>
   <si>
-    <t>Иванов Иван</t>
-  </si>
-  <si>
-    <t>+79001234567</t>
-  </si>
-  <si>
-    <t>info@trans.ru</t>
-  </si>
-  <si>
     <t>ООО</t>
   </si>
   <si>
@@ -261,12 +207,6 @@
   </si>
   <si>
     <t>0-MPPEE-2605-20-10-001</t>
-  </si>
-  <si>
-    <t>Новый рейс 1</t>
-  </si>
-  <si>
-    <t>Новый рейс 2</t>
   </si>
   <si>
     <t>ФТК СОТРАНС</t>
@@ -279,20 +219,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF444444"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -387,27 +320,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,216 +639,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="9" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="13" width="18" customWidth="1"/>
-    <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="30" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-    </row>
-    <row r="2" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="3">
         <v>22</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O3" s="2"/>
-    </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="3">
+        <v>42916</v>
+      </c>
+      <c r="E3" s="3">
+        <v>52357.52</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>82</v>
+        <v>63</v>
+      </c>
+      <c r="C4" s="3">
+        <v>22</v>
       </c>
       <c r="D4" s="3">
-        <v>7802355025</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="3">
-        <v>22</v>
-      </c>
-      <c r="I4" s="3">
-        <v>42916</v>
-      </c>
-      <c r="J4" s="3">
-        <v>52357.52</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-    </row>
-    <row r="5" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="3">
-        <v>9703020247</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="3">
-        <v>22</v>
-      </c>
-      <c r="I5" s="3">
         <v>15000</v>
       </c>
-      <c r="J5" s="3">
+      <c r="E4" s="3">
         <v>15750</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -935,7 +745,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -943,47 +753,47 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -991,55 +801,55 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
@@ -1047,55 +857,55 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="7" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -1103,31 +913,31 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
@@ -1135,23 +945,23 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="7" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
